--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308850</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308833</v>
       </c>
       <c r="B3" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308849</v>
       </c>
       <c r="B4" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308824</v>
       </c>
       <c r="B5" t="n">
-        <v>78872</v>
+        <v>78875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308829</v>
       </c>
       <c r="B8" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308844</v>
       </c>
       <c r="B13" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308846</v>
       </c>
       <c r="B14" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308835</v>
       </c>
       <c r="B15" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308842</v>
       </c>
       <c r="B16" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308843</v>
       </c>
       <c r="B17" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308860</v>
       </c>
       <c r="B18" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308825</v>
       </c>
       <c r="B19" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308851</v>
       </c>
       <c r="B20" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308853</v>
       </c>
       <c r="B21" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137308827</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137308834</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137308859</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137308828</v>
       </c>
       <c r="B27" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308862</v>
       </c>
       <c r="B28" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308857</v>
       </c>
       <c r="B29" t="n">
-        <v>78871</v>
+        <v>78874</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308832</v>
       </c>
       <c r="B30" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308838</v>
       </c>
       <c r="B31" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308848</v>
       </c>
       <c r="B32" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308831</v>
       </c>
       <c r="B33" t="n">
-        <v>83502</v>
+        <v>83505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308836</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>137308852</v>
       </c>
       <c r="B35" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137308845</v>
       </c>
       <c r="B36" t="n">
-        <v>80584</v>
+        <v>80587</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308850</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308833</v>
       </c>
       <c r="B3" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308849</v>
       </c>
       <c r="B4" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308824</v>
       </c>
       <c r="B5" t="n">
-        <v>78875</v>
+        <v>78880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308829</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308844</v>
       </c>
       <c r="B13" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308846</v>
       </c>
       <c r="B14" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308835</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308842</v>
       </c>
       <c r="B16" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308843</v>
       </c>
       <c r="B17" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308860</v>
       </c>
       <c r="B18" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308825</v>
       </c>
       <c r="B19" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308851</v>
       </c>
       <c r="B20" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308853</v>
       </c>
       <c r="B21" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137308827</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137308834</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137308859</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137308828</v>
       </c>
       <c r="B27" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308862</v>
       </c>
       <c r="B28" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308857</v>
       </c>
       <c r="B29" t="n">
-        <v>78874</v>
+        <v>78879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308832</v>
       </c>
       <c r="B30" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308838</v>
       </c>
       <c r="B31" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308848</v>
       </c>
       <c r="B32" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308831</v>
       </c>
       <c r="B33" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308836</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>137308852</v>
       </c>
       <c r="B35" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137308845</v>
       </c>
       <c r="B36" t="n">
-        <v>80587</v>
+        <v>80592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308850</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308833</v>
       </c>
       <c r="B3" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308849</v>
       </c>
       <c r="B4" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308824</v>
       </c>
       <c r="B5" t="n">
-        <v>78880</v>
+        <v>78891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308829</v>
       </c>
       <c r="B8" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308844</v>
       </c>
       <c r="B13" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308846</v>
       </c>
       <c r="B14" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308835</v>
       </c>
       <c r="B15" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308842</v>
       </c>
       <c r="B16" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308843</v>
       </c>
       <c r="B17" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308860</v>
       </c>
       <c r="B18" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308825</v>
       </c>
       <c r="B19" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308851</v>
       </c>
       <c r="B20" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308853</v>
       </c>
       <c r="B21" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137308827</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137308834</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137308859</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137308828</v>
       </c>
       <c r="B27" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308862</v>
       </c>
       <c r="B28" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308857</v>
       </c>
       <c r="B29" t="n">
-        <v>78879</v>
+        <v>78890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308832</v>
       </c>
       <c r="B30" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308838</v>
       </c>
       <c r="B31" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308848</v>
       </c>
       <c r="B32" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308831</v>
       </c>
       <c r="B33" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>137308852</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137308845</v>
       </c>
       <c r="B36" t="n">
-        <v>80592</v>
+        <v>80603</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308850</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308833</v>
       </c>
       <c r="B3" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308849</v>
       </c>
       <c r="B4" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308824</v>
       </c>
       <c r="B5" t="n">
-        <v>78891</v>
+        <v>78892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308829</v>
       </c>
       <c r="B8" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308844</v>
       </c>
       <c r="B13" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308846</v>
       </c>
       <c r="B14" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308835</v>
       </c>
       <c r="B15" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308842</v>
       </c>
       <c r="B16" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308843</v>
       </c>
       <c r="B17" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308860</v>
       </c>
       <c r="B18" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308825</v>
       </c>
       <c r="B19" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308851</v>
       </c>
       <c r="B20" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308853</v>
       </c>
       <c r="B21" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137308827</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137308834</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137308859</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137308828</v>
       </c>
       <c r="B27" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308862</v>
       </c>
       <c r="B28" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308857</v>
       </c>
       <c r="B29" t="n">
-        <v>78890</v>
+        <v>78891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308832</v>
       </c>
       <c r="B30" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308838</v>
       </c>
       <c r="B31" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308848</v>
       </c>
       <c r="B32" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308831</v>
       </c>
       <c r="B33" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>137308852</v>
       </c>
       <c r="B35" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137308845</v>
       </c>
       <c r="B36" t="n">
-        <v>80603</v>
+        <v>80604</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308850</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308833</v>
       </c>
       <c r="B3" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308849</v>
       </c>
       <c r="B4" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308824</v>
       </c>
       <c r="B5" t="n">
-        <v>78892</v>
+        <v>78894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308829</v>
       </c>
       <c r="B8" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308844</v>
       </c>
       <c r="B13" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308846</v>
       </c>
       <c r="B14" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308835</v>
       </c>
       <c r="B15" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308842</v>
       </c>
       <c r="B16" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308843</v>
       </c>
       <c r="B17" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308860</v>
       </c>
       <c r="B18" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308825</v>
       </c>
       <c r="B19" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308851</v>
       </c>
       <c r="B20" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308853</v>
       </c>
       <c r="B21" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137308827</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137308834</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137308859</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137308828</v>
       </c>
       <c r="B27" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308862</v>
       </c>
       <c r="B28" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308857</v>
       </c>
       <c r="B29" t="n">
-        <v>78891</v>
+        <v>78893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308832</v>
       </c>
       <c r="B30" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308838</v>
       </c>
       <c r="B31" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308848</v>
       </c>
       <c r="B32" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308831</v>
       </c>
       <c r="B33" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>137308852</v>
       </c>
       <c r="B35" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137308845</v>
       </c>
       <c r="B36" t="n">
-        <v>80604</v>
+        <v>80606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 14893-2026 artfynd.xlsx
+++ b/artfynd/A 14893-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137308850</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137308833</v>
       </c>
       <c r="B3" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137308849</v>
       </c>
       <c r="B4" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137308824</v>
       </c>
       <c r="B5" t="n">
-        <v>78894</v>
+        <v>78898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137308826</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137308855</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137308829</v>
       </c>
       <c r="B8" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137308839</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137308841</v>
       </c>
       <c r="B10" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137308856</v>
       </c>
       <c r="B11" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137308847</v>
       </c>
       <c r="B12" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137308844</v>
       </c>
       <c r="B13" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137308846</v>
       </c>
       <c r="B14" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137308835</v>
       </c>
       <c r="B15" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>137308842</v>
       </c>
       <c r="B16" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>137308843</v>
       </c>
       <c r="B17" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137308860</v>
       </c>
       <c r="B18" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>137308825</v>
       </c>
       <c r="B19" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137308851</v>
       </c>
       <c r="B20" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>137308853</v>
       </c>
       <c r="B21" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137308840</v>
       </c>
       <c r="B22" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>137308830</v>
       </c>
       <c r="B23" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>137308827</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>137308834</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>137308859</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137308828</v>
       </c>
       <c r="B27" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>137308862</v>
       </c>
       <c r="B28" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137308857</v>
       </c>
       <c r="B29" t="n">
-        <v>78893</v>
+        <v>78897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137308832</v>
       </c>
       <c r="B30" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>137308838</v>
       </c>
       <c r="B31" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>137308848</v>
       </c>
       <c r="B32" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>137308831</v>
       </c>
       <c r="B33" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>137308836</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>137308852</v>
       </c>
       <c r="B35" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137308845</v>
       </c>
       <c r="B36" t="n">
-        <v>80606</v>
+        <v>80610</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
